--- a/Code/data/reports/TS2_558.xlsx
+++ b/Code/data/reports/TS2_558.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Budget Report" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,16 +19,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="₹ #,##0.00;[Red]₹ -#,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Bookman Old Style"/>
@@ -56,7 +53,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -64,21 +61,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
